--- a/docs/deliverables/out/Drop-1_Transactional/TestPlans/BIBS_TestPlan_BRD-02_Operations_v1.0.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/TestPlans/BIBS_TestPlan_BRD-02_Operations_v1.0.xlsx
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Role code and name (and demo user for built BRDs)</t>
+          <t>Role code and name (and SIT/UAT user for built BRDs)</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Demo seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
+          <t>Seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr"/>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -9424,7 +9424,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Demo users TD-OP-01; booked invoices TD-OP-02.</t>
+          <t>SIT/UAT users TD-OP-01; booked invoices TD-OP-02.</t>
         </is>
       </c>
       <c r="F5" s="12" t="n">
@@ -9444,7 +9444,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -9594,7 +9594,7 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-01 Demo users and roles</t>
+          <t>Data: TD-OP-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J5" s="12" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-01 Demo users and roles</t>
+          <t>Data: TD-OP-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
@@ -10036,7 +10036,7 @@
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -10047,7 +10047,7 @@
       <c r="I7" s="12" t="inlineStr">
         <is>
           <t>LOGIN_MAX_FAILED_ATTEMPTS is 3.
-Data: TD-OP-01 Demo users and roles</t>
+Data: TD-OP-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J7" s="12" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-01 Demo users and roles</t>
+          <t>Data: TD-OP-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J8" s="12" t="inlineStr">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
@@ -10200,7 +10200,7 @@
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-01 Demo users and roles</t>
+          <t>Data: TD-OP-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J9" s="12" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
@@ -10277,7 +10277,7 @@
       </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-01 Demo users and roles</t>
+          <t>Data: TD-OP-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J10" s="12" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-01 Demo users and roles</t>
+          <t>Data: TD-OP-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance TL / TH (demo user remittl)</t>
+          <t>REMIT_TL – Remittance TL / TH (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-01 Demo users and roles</t>
+          <t>Data: TD-OP-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J12" s="12" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>COMPTROLLERSHIP – Comptrollership (demo user comptrol)</t>
+          <t>COMPTROLLERSHIP – Comptrollership (SIT/UAT user comptrol)</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-01 Demo users and roles</t>
+          <t>Data: TD-OP-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J13" s="12" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
@@ -10579,7 +10579,7 @@
       <c r="I14" s="12" t="inlineStr">
         <is>
           <t>An account booked in this cycle (TC-NB-110.1-01 of the BRD-1 plan).
-Data: TD-OP-02 Booked demo invoices</t>
+Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J14" s="12" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
@@ -10655,7 +10655,7 @@
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J15" s="12" t="inlineStr">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J16" s="12" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J17" s="12" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
@@ -10884,7 +10884,7 @@
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices; TD-OP-04 Remittance storyline</t>
+          <t>Data: TD-OP-02 Booked seed invoices; TD-OP-04 Remittance storyline</t>
         </is>
       </c>
       <c r="J18" s="12" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -10961,7 +10961,7 @@
       <c r="I19" s="12" t="inlineStr">
         <is>
           <t>The hold of ARN-2026-940004 approved (TC-OP-111.1-01).
-Data: TD-OP-02 Booked demo invoices; TD-OP-04 Remittance storyline</t>
+Data: TD-OP-02 Booked seed invoices; TD-OP-04 Remittance storyline</t>
         </is>
       </c>
       <c r="J19" s="12" t="inlineStr">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
@@ -11033,7 +11033,7 @@
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices; TD-OP-04 Remittance storyline</t>
+          <t>Data: TD-OP-02 Booked seed invoices; TD-OP-04 Remittance storyline</t>
         </is>
       </c>
       <c r="J20" s="12" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices; TD-OP-04 Remittance storyline</t>
+          <t>Data: TD-OP-02 Booked seed invoices; TD-OP-04 Remittance storyline</t>
         </is>
       </c>
       <c r="J21" s="12" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices; TD-OP-04 Remittance storyline</t>
+          <t>Data: TD-OP-02 Booked seed invoices; TD-OP-04 Remittance storyline</t>
         </is>
       </c>
       <c r="J22" s="12" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
@@ -11258,7 +11258,7 @@
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices; TD-OP-04 Remittance storyline</t>
+          <t>Data: TD-OP-02 Booked seed invoices; TD-OP-04 Remittance storyline</t>
         </is>
       </c>
       <c r="J23" s="12" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H24" s="12" t="inlineStr">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices; TD-OP-04 Remittance storyline</t>
+          <t>Data: TD-OP-02 Booked seed invoices; TD-OP-04 Remittance storyline</t>
         </is>
       </c>
       <c r="J24" s="12" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -11917,7 +11917,7 @@
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -12066,7 +12066,7 @@
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>CASHIER_BR – Cashier (branch (demo user cashbr)</t>
+          <t>CASHIER_BR – Cashier (branch (SIT/UAT user cashbr)</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
@@ -12218,7 +12218,7 @@
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>CASHIER_TL – Cashiering TL / TH (demo user cashtl)</t>
+          <t>CASHIER_TL – Cashiering TL / TH (SIT/UAT user cashtl)</t>
         </is>
       </c>
       <c r="H36" s="12" t="inlineStr">
@@ -12295,7 +12295,7 @@
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>CASHIER_TL – Cashiering TL / TH (demo user cashtl)</t>
+          <t>CASHIER_TL – Cashiering TL / TH (SIT/UAT user cashtl)</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -12368,7 +12368,7 @@
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>CASHIER_TL – Cashiering TL / TH (demo user cashtl)</t>
+          <t>CASHIER_TL – Cashiering TL / TH (SIT/UAT user cashtl)</t>
         </is>
       </c>
       <c r="H38" s="12" t="inlineStr">
@@ -12445,7 +12445,7 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>CASHIER_BR – Cashier (branch (demo user cashbr)</t>
+          <t>CASHIER_BR – Cashier (branch (SIT/UAT user cashbr)</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H40" s="12" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices; TD-OP-09 USD receipt and BOOK rates</t>
+          <t>Data: TD-OP-02 Booked seed invoices; TD-OP-09 USD receipt and BOOK rates</t>
         </is>
       </c>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>1. Receive Payment; AR class OTC; invoice of a booked demo account; amount = outstanding; mode cash; preview; post.</t>
+          <t>1. Receive Payment; AR class OTC; invoice of a booked seed account; amount = outstanding; mode cash; preview; post.</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
@@ -12675,7 +12675,7 @@
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H42" s="12" t="inlineStr">
@@ -12685,7 +12685,7 @@
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices; TD-OP-09 USD receipt and BOOK rates</t>
+          <t>Data: TD-OP-02 Booked seed invoices; TD-OP-09 USD receipt and BOOK rates</t>
         </is>
       </c>
       <c r="J42" s="12" t="inlineStr">
@@ -12751,7 +12751,7 @@
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices; TD-OP-09 USD receipt and BOOK rates</t>
+          <t>Data: TD-OP-02 Booked seed invoices; TD-OP-09 USD receipt and BOOK rates</t>
         </is>
       </c>
       <c r="J43" s="12" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices; TD-OP-09 USD receipt and BOOK rates</t>
+          <t>Data: TD-OP-02 Booked seed invoices; TD-OP-09 USD receipt and BOOK rates</t>
         </is>
       </c>
       <c r="J44" s="12" t="inlineStr">
@@ -12896,7 +12896,7 @@
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H45" s="12" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>CASHIER_BR – Cashier (branch (demo user cashbr)</t>
+          <t>CASHIER_BR – Cashier (branch (SIT/UAT user cashbr)</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H47" s="12" t="inlineStr">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H48" s="12" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>CASHIER_TL – Cashiering TL / TH (demo user cashtl)</t>
+          <t>CASHIER_TL – Cashiering TL / TH (SIT/UAT user cashtl)</t>
         </is>
       </c>
       <c r="H49" s="12" t="inlineStr">
@@ -13277,7 +13277,7 @@
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H50" s="12" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H51" s="12" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H52" s="12" t="inlineStr">
@@ -13507,7 +13507,7 @@
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H53" s="12" t="inlineStr">
@@ -13584,7 +13584,7 @@
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H54" s="12" t="inlineStr">
@@ -13657,7 +13657,7 @@
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H55" s="12" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H56" s="12" t="inlineStr">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H57" s="12" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
-          <t>CASHIER_TL – Cashiering TL / TH (demo user cashtl)</t>
+          <t>CASHIER_TL – Cashiering TL / TH (SIT/UAT user cashtl)</t>
         </is>
       </c>
       <c r="H58" s="12" t="inlineStr">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>CASHIER_TL – Cashiering TL / TH (demo user cashtl)</t>
+          <t>CASHIER_TL – Cashiering TL / TH (SIT/UAT user cashtl)</t>
         </is>
       </c>
       <c r="H59" s="12" t="inlineStr">
@@ -14036,7 +14036,7 @@
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H60" s="12" t="inlineStr">
@@ -14112,7 +14112,7 @@
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H61" s="12" t="inlineStr">
@@ -14127,7 +14127,7 @@
       </c>
       <c r="J61" s="12" t="inlineStr">
         <is>
-          <t>1. Add the demo PDC again with the same bank and check number.</t>
+          <t>1. Add the seed PDC again with the same bank and check number.</t>
         </is>
       </c>
       <c r="K61" s="12" t="inlineStr">
@@ -14185,7 +14185,7 @@
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H62" s="12" t="inlineStr">
@@ -14258,7 +14258,7 @@
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H63" s="12" t="inlineStr">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H64" s="12" t="inlineStr">
@@ -14344,7 +14344,7 @@
       </c>
       <c r="I64" s="12" t="inlineStr">
         <is>
-          <t>The two demo requests are due today (dates moved in SIT).
+          <t>The two seed requests are due today (dates moved in SIT).
 Data: TD-OP-03 Cashiering storyline</t>
         </is>
       </c>
@@ -14411,7 +14411,7 @@
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H65" s="12" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H66" s="12" t="inlineStr">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H67" s="12" t="inlineStr">
@@ -14575,7 +14575,7 @@
       </c>
       <c r="I67" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices; TD-OP-03 Cashiering storyline</t>
+          <t>Data: TD-OP-02 Booked seed invoices; TD-OP-03 Cashiering storyline</t>
         </is>
       </c>
       <c r="J67" s="12" t="inlineStr">
@@ -14641,7 +14641,7 @@
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H68" s="12" t="inlineStr">
@@ -14651,7 +14651,7 @@
       </c>
       <c r="I68" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices; TD-OP-03 Cashiering storyline</t>
+          <t>Data: TD-OP-02 Booked seed invoices; TD-OP-03 Cashiering storyline</t>
         </is>
       </c>
       <c r="J68" s="12" t="inlineStr">
@@ -14717,7 +14717,7 @@
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H69" s="12" t="inlineStr">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="I69" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices; TD-OP-03 Cashiering storyline</t>
+          <t>Data: TD-OP-02 Booked seed invoices; TD-OP-03 Cashiering storyline</t>
         </is>
       </c>
       <c r="J69" s="12" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H70" s="12" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="I70" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices; TD-OP-03 Cashiering storyline</t>
+          <t>Data: TD-OP-02 Booked seed invoices; TD-OP-03 Cashiering storyline</t>
         </is>
       </c>
       <c r="J70" s="12" t="inlineStr">
@@ -14865,7 +14865,7 @@
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H71" s="12" t="inlineStr">
@@ -14875,7 +14875,7 @@
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices; TD-OP-03 Cashiering storyline</t>
+          <t>Data: TD-OP-02 Booked seed invoices; TD-OP-03 Cashiering storyline</t>
         </is>
       </c>
       <c r="J71" s="12" t="inlineStr">
@@ -14938,7 +14938,7 @@
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H72" s="12" t="inlineStr">
@@ -14948,7 +14948,7 @@
       </c>
       <c r="I72" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J72" s="12" t="inlineStr">
@@ -15014,7 +15014,7 @@
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H73" s="12" t="inlineStr">
@@ -15024,7 +15024,7 @@
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J73" s="12" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H74" s="12" t="inlineStr">
@@ -15100,7 +15100,7 @@
       </c>
       <c r="I74" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J74" s="12" t="inlineStr">
@@ -15166,7 +15166,7 @@
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H75" s="12" t="inlineStr">
@@ -15238,7 +15238,7 @@
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H76" s="12" t="inlineStr">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H77" s="12" t="inlineStr">
@@ -15387,7 +15387,7 @@
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance TL / TH (demo user remittl)</t>
+          <t>REMIT_TL – Remittance TL / TH (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H78" s="12" t="inlineStr">
@@ -15402,7 +15402,7 @@
       </c>
       <c r="J78" s="12" t="inlineStr">
         <is>
-          <t>1. Open the remitted demo batch of ARN-2026-940001.</t>
+          <t>1. Open the remitted seed batch of ARN-2026-940001.</t>
         </is>
       </c>
       <c r="K78" s="12" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H79" s="12" t="inlineStr">
@@ -15535,7 +15535,7 @@
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H80" s="12" t="inlineStr">
@@ -15608,7 +15608,7 @@
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H81" s="12" t="inlineStr">
@@ -15684,7 +15684,7 @@
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H82" s="12" t="inlineStr">
@@ -15699,7 +15699,7 @@
       </c>
       <c r="J82" s="12" t="inlineStr">
         <is>
-          <t>1. Open the demo item with the refund for approval; as cashtl click Approve; as disb pay it in the Disbursement Queue.</t>
+          <t>1. Open the seed item with the refund for approval; as cashtl click Approve; as disb pay it in the Disbursement Queue.</t>
         </is>
       </c>
       <c r="K82" s="12" t="inlineStr">
@@ -15760,7 +15760,7 @@
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
-          <t>CASHIER_TL – Cashiering TL / TH (demo user cashtl)</t>
+          <t>CASHIER_TL – Cashiering TL / TH (SIT/UAT user cashtl)</t>
         </is>
       </c>
       <c r="H83" s="12" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H84" s="12" t="inlineStr">
@@ -15907,7 +15907,7 @@
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H85" s="12" t="inlineStr">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H86" s="12" t="inlineStr">
@@ -16004,7 +16004,7 @@
       </c>
       <c r="K86" s="12" t="inlineStr">
         <is>
-          <t>Each demo item is in the tab of its stage.</t>
+          <t>Each seed item is in the tab of its stage.</t>
         </is>
       </c>
       <c r="L86" s="12" t="inlineStr">
@@ -16056,7 +16056,7 @@
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>CASHIER_TL – Cashiering TL / TH (demo user cashtl)</t>
+          <t>CASHIER_TL – Cashiering TL / TH (SIT/UAT user cashtl)</t>
         </is>
       </c>
       <c r="H87" s="12" t="inlineStr">
@@ -16132,7 +16132,7 @@
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
-          <t>CASHIER_TL – Cashiering TL / TH (demo user cashtl)</t>
+          <t>CASHIER_TL – Cashiering TL / TH (SIT/UAT user cashtl)</t>
         </is>
       </c>
       <c r="H88" s="12" t="inlineStr">
@@ -16208,7 +16208,7 @@
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
-          <t>CASHIER_TL – Cashiering TL / TH (demo user cashtl)</t>
+          <t>CASHIER_TL – Cashiering TL / TH (SIT/UAT user cashtl)</t>
         </is>
       </c>
       <c r="H89" s="12" t="inlineStr">
@@ -16284,7 +16284,7 @@
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H90" s="12" t="inlineStr">
@@ -16356,7 +16356,7 @@
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H91" s="12" t="inlineStr">
@@ -16432,7 +16432,7 @@
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="H92" s="12" t="inlineStr">
@@ -16508,7 +16508,7 @@
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H93" s="12" t="inlineStr">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H94" s="12" t="inlineStr">
@@ -16661,7 +16661,7 @@
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H95" s="12" t="inlineStr">
@@ -16734,7 +16734,7 @@
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H96" s="12" t="inlineStr">
@@ -16810,7 +16810,7 @@
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H97" s="12" t="inlineStr">
@@ -16883,7 +16883,7 @@
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H98" s="12" t="inlineStr">
@@ -16960,7 +16960,7 @@
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H99" s="12" t="inlineStr">
@@ -17036,7 +17036,7 @@
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
-          <t>COMPTROLLERSHIP – Comptrollership (demo user comptrol)</t>
+          <t>COMPTROLLERSHIP – Comptrollership (SIT/UAT user comptrol)</t>
         </is>
       </c>
       <c r="H100" s="12" t="inlineStr">
@@ -17112,7 +17112,7 @@
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
-          <t>COMPTROLLERSHIP – Comptrollership (demo user comptrol)</t>
+          <t>COMPTROLLERSHIP – Comptrollership (SIT/UAT user comptrol)</t>
         </is>
       </c>
       <c r="H101" s="12" t="inlineStr">
@@ -17184,7 +17184,7 @@
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H102" s="12" t="inlineStr">
@@ -17258,7 +17258,7 @@
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H103" s="12" t="inlineStr">
@@ -17334,7 +17334,7 @@
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H104" s="12" t="inlineStr">
@@ -17410,7 +17410,7 @@
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H105" s="12" t="inlineStr">
@@ -17483,7 +17483,7 @@
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H106" s="12" t="inlineStr">
@@ -17494,7 +17494,7 @@
       <c r="I106" s="12" t="inlineStr">
         <is>
           <t>An invoice of INS-MGIC paid in cash four banking days ago.
-Data: TD-OP-02 Booked demo invoices; TD-OP-04 Remittance storyline</t>
+Data: TD-OP-02 Booked seed invoices; TD-OP-04 Remittance storyline</t>
         </is>
       </c>
       <c r="J106" s="12" t="inlineStr">
@@ -17560,7 +17560,7 @@
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H107" s="12" t="inlineStr">
@@ -17571,7 +17571,7 @@
       <c r="I107" s="12" t="inlineStr">
         <is>
           <t>The hold of ARN-2026-940004 approved.
-Data: TD-OP-02 Booked demo invoices; TD-OP-04 Remittance storyline</t>
+Data: TD-OP-02 Booked seed invoices; TD-OP-04 Remittance storyline</t>
         </is>
       </c>
       <c r="J107" s="12" t="inlineStr">
@@ -17637,7 +17637,7 @@
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H108" s="12" t="inlineStr">
@@ -17647,7 +17647,7 @@
       </c>
       <c r="I108" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices; TD-OP-04 Remittance storyline</t>
+          <t>Data: TD-OP-02 Booked seed invoices; TD-OP-04 Remittance storyline</t>
         </is>
       </c>
       <c r="J108" s="12" t="inlineStr">
@@ -17714,7 +17714,7 @@
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H109" s="12" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices; TD-OP-04 Remittance storyline</t>
+          <t>Data: TD-OP-02 Booked seed invoices; TD-OP-04 Remittance storyline</t>
         </is>
       </c>
       <c r="J109" s="12" t="inlineStr">
@@ -17791,7 +17791,7 @@
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H110" s="12" t="inlineStr">
@@ -17801,7 +17801,7 @@
       </c>
       <c r="I110" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices; TD-OP-04 Remittance storyline</t>
+          <t>Data: TD-OP-02 Booked seed invoices; TD-OP-04 Remittance storyline</t>
         </is>
       </c>
       <c r="J110" s="12" t="inlineStr">
@@ -17867,7 +17867,7 @@
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H111" s="12" t="inlineStr">
@@ -17877,7 +17877,7 @@
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J111" s="12" t="inlineStr">
@@ -17943,7 +17943,7 @@
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H112" s="12" t="inlineStr">
@@ -17954,7 +17954,7 @@
       <c r="I112" s="12" t="inlineStr">
         <is>
           <t>An invoice with paid AR 10,500.00 and DTIP 10,000.00; REMIT_PAIDAR_OVER_DTIP_MODE = EXCLUDE.
-Data: TD-OP-02 Booked demo invoices</t>
+Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J112" s="12" t="inlineStr">
@@ -18020,7 +18020,7 @@
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H113" s="12" t="inlineStr">
@@ -18030,7 +18030,7 @@
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J113" s="12" t="inlineStr">
@@ -18096,7 +18096,7 @@
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H114" s="12" t="inlineStr">
@@ -18107,7 +18107,7 @@
       <c r="I114" s="12" t="inlineStr">
         <is>
           <t>An invoice written off by the minimal balance file (TC-OP-059.1-01).
-Data: TD-OP-02 Booked demo invoices</t>
+Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J114" s="12" t="inlineStr">
@@ -18173,7 +18173,7 @@
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H115" s="12" t="inlineStr">
@@ -18183,7 +18183,7 @@
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J115" s="12" t="inlineStr">
@@ -18249,7 +18249,7 @@
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H116" s="12" t="inlineStr">
@@ -18325,7 +18325,7 @@
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H117" s="12" t="inlineStr">
@@ -18401,7 +18401,7 @@
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H118" s="12" t="inlineStr">
@@ -18474,7 +18474,7 @@
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H119" s="12" t="inlineStr">
@@ -18547,7 +18547,7 @@
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H120" s="12" t="inlineStr">
@@ -18620,7 +18620,7 @@
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H121" s="12" t="inlineStr">
@@ -18696,7 +18696,7 @@
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H122" s="12" t="inlineStr">
@@ -18769,7 +18769,7 @@
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance TL / TH (demo user remittl)</t>
+          <t>REMIT_TL – Remittance TL / TH (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H123" s="12" t="inlineStr">
@@ -18845,7 +18845,7 @@
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H124" s="12" t="inlineStr">
@@ -18860,7 +18860,7 @@
       </c>
       <c r="J124" s="12" t="inlineStr">
         <is>
-          <t>1. Open the remitted demo batch; Documents; download the schedule.</t>
+          <t>1. Open the remitted seed batch; Documents; download the schedule.</t>
         </is>
       </c>
       <c r="K124" s="12" t="inlineStr">
@@ -18921,7 +18921,7 @@
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H125" s="12" t="inlineStr">
@@ -18997,7 +18997,7 @@
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H126" s="12" t="inlineStr">
@@ -19069,7 +19069,7 @@
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance TL / TH (demo user remittl)</t>
+          <t>REMIT_TL – Remittance TL / TH (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H127" s="12" t="inlineStr">
@@ -19143,7 +19143,7 @@
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance TL / TH (demo user remittl)</t>
+          <t>REMIT_TL – Remittance TL / TH (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H128" s="12" t="inlineStr">
@@ -19219,7 +19219,7 @@
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance TL / TH (demo user remittl)</t>
+          <t>REMIT_TL – Remittance TL / TH (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H129" s="12" t="inlineStr">
@@ -19292,7 +19292,7 @@
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H130" s="12" t="inlineStr">
@@ -19368,7 +19368,7 @@
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H131" s="12" t="inlineStr">
@@ -19440,7 +19440,7 @@
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H132" s="12" t="inlineStr">
@@ -19516,7 +19516,7 @@
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H133" s="12" t="inlineStr">
@@ -19592,7 +19592,7 @@
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H134" s="12" t="inlineStr">
@@ -19668,7 +19668,7 @@
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H135" s="12" t="inlineStr">
@@ -19741,7 +19741,7 @@
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H136" s="12" t="inlineStr">
@@ -19814,7 +19814,7 @@
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance TL / TH (demo user remittl)</t>
+          <t>REMIT_TL – Remittance TL / TH (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H137" s="12" t="inlineStr">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance TL / TH (demo user remittl)</t>
+          <t>REMIT_TL – Remittance TL / TH (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H138" s="12" t="inlineStr">
@@ -19967,7 +19967,7 @@
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance TL / TH (demo user remittl)</t>
+          <t>REMIT_TL – Remittance TL / TH (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H139" s="12" t="inlineStr">
@@ -20044,7 +20044,7 @@
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H140" s="12" t="inlineStr">
@@ -20054,7 +20054,7 @@
       </c>
       <c r="I140" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices; TD-OP-04 Remittance storyline</t>
+          <t>Data: TD-OP-02 Booked seed invoices; TD-OP-04 Remittance storyline</t>
         </is>
       </c>
       <c r="J140" s="12" t="inlineStr">
@@ -20116,7 +20116,7 @@
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H141" s="12" t="inlineStr">
@@ -20126,12 +20126,12 @@
       </c>
       <c r="I141" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices; TD-OP-04 Remittance storyline</t>
+          <t>Data: TD-OP-02 Booked seed invoices; TD-OP-04 Remittance storyline</t>
         </is>
       </c>
       <c r="J141" s="12" t="inlineStr">
         <is>
-          <t>1. Search the number of the remitted demo batch.</t>
+          <t>1. Search the number of the remitted seed batch.</t>
         </is>
       </c>
       <c r="K141" s="12" t="inlineStr">
@@ -20188,7 +20188,7 @@
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H142" s="12" t="inlineStr">
@@ -20198,7 +20198,7 @@
       </c>
       <c r="I142" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices; TD-OP-04 Remittance storyline</t>
+          <t>Data: TD-OP-02 Booked seed invoices; TD-OP-04 Remittance storyline</t>
         </is>
       </c>
       <c r="J142" s="12" t="inlineStr">
@@ -20265,7 +20265,7 @@
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance TL / TH (demo user remittl)</t>
+          <t>REMIT_TL – Remittance TL / TH (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H143" s="12" t="inlineStr">
@@ -20280,7 +20280,7 @@
       </c>
       <c r="J143" s="12" t="inlineStr">
         <is>
-          <t>1. Open the demo request for approval; click Approve special remittance; approve its batch.</t>
+          <t>1. Open the seed request for approval; click Approve special remittance; approve its batch.</t>
         </is>
       </c>
       <c r="K143" s="12" t="inlineStr">
@@ -20341,7 +20341,7 @@
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance TL / TH (demo user remittl)</t>
+          <t>REMIT_TL – Remittance TL / TH (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H144" s="12" t="inlineStr">
@@ -20415,7 +20415,7 @@
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance TL / TH (demo user remittl)</t>
+          <t>REMIT_TL – Remittance TL / TH (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H145" s="12" t="inlineStr">
@@ -20491,7 +20491,7 @@
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H146" s="12" t="inlineStr">
@@ -20511,7 +20511,7 @@
       </c>
       <c r="K146" s="12" t="inlineStr">
         <is>
-          <t>One row per batch with the columns; the remitted demo batch is listed.</t>
+          <t>One row per batch with the columns; the remitted seed batch is listed.</t>
         </is>
       </c>
       <c r="L146" s="12" t="inlineStr">
@@ -20567,7 +20567,7 @@
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H147" s="12" t="inlineStr">
@@ -20643,7 +20643,7 @@
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H148" s="12" t="inlineStr">
@@ -20716,7 +20716,7 @@
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H149" s="12" t="inlineStr">
@@ -20726,12 +20726,12 @@
       </c>
       <c r="I149" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J149" s="12" t="inlineStr">
         <is>
-          <t>1. New Request; invoice of a paid demo account; type flat cancellation; reason Unit sold; effective date within cover; description; Submit for validation.</t>
+          <t>1. New Request; invoice of a paid seed account; type flat cancellation; reason Unit sold; effective date within cover; description; Submit for validation.</t>
         </is>
       </c>
       <c r="K149" s="12" t="inlineStr">
@@ -20792,7 +20792,7 @@
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H150" s="12" t="inlineStr">
@@ -20802,7 +20802,7 @@
       </c>
       <c r="I150" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J150" s="12" t="inlineStr">
@@ -20869,7 +20869,7 @@
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H151" s="12" t="inlineStr">
@@ -20879,7 +20879,7 @@
       </c>
       <c r="I151" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J151" s="12" t="inlineStr">
@@ -20945,7 +20945,7 @@
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H152" s="12" t="inlineStr">
@@ -20955,7 +20955,7 @@
       </c>
       <c r="I152" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J152" s="12" t="inlineStr">
@@ -21017,7 +21017,7 @@
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H153" s="12" t="inlineStr">
@@ -21027,7 +21027,7 @@
       </c>
       <c r="I153" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J153" s="12" t="inlineStr">
@@ -21094,7 +21094,7 @@
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H154" s="12" t="inlineStr">
@@ -21104,7 +21104,7 @@
       </c>
       <c r="I154" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J154" s="12" t="inlineStr">
@@ -21171,7 +21171,7 @@
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H155" s="12" t="inlineStr">
@@ -21181,7 +21181,7 @@
       </c>
       <c r="I155" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J155" s="12" t="inlineStr">
@@ -21248,7 +21248,7 @@
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H156" s="12" t="inlineStr">
@@ -21263,7 +21263,7 @@
       </c>
       <c r="J156" s="12" t="inlineStr">
         <is>
-          <t>1. Raise a flat cancellation on ARN-2026-940004 with reason Unit sold (the demo one is open).</t>
+          <t>1. Raise a flat cancellation on ARN-2026-940004 with reason Unit sold (the seed one is open).</t>
         </is>
       </c>
       <c r="K156" s="12" t="inlineStr">
@@ -21325,7 +21325,7 @@
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H157" s="12" t="inlineStr">
@@ -21401,7 +21401,7 @@
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H158" s="12" t="inlineStr">
@@ -21477,7 +21477,7 @@
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H159" s="12" t="inlineStr">
@@ -21554,7 +21554,7 @@
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT_TL – Adjustment TL (demo user adjtl)</t>
+          <t>ADJUSTMENT_TL – Adjustment TL (SIT/UAT user adjtl)</t>
         </is>
       </c>
       <c r="H160" s="12" t="inlineStr">
@@ -21632,7 +21632,7 @@
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT_TL – Adjustment TL (demo user adjtl)</t>
+          <t>ADJUSTMENT_TL – Adjustment TL (SIT/UAT user adjtl)</t>
         </is>
       </c>
       <c r="H161" s="12" t="inlineStr">
@@ -21708,7 +21708,7 @@
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H162" s="12" t="inlineStr">
@@ -21781,7 +21781,7 @@
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H163" s="12" t="inlineStr">
@@ -21857,7 +21857,7 @@
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H164" s="12" t="inlineStr">
@@ -21930,7 +21930,7 @@
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H165" s="12" t="inlineStr">
@@ -22006,7 +22006,7 @@
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H166" s="12" t="inlineStr">
@@ -22082,7 +22082,7 @@
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H167" s="12" t="inlineStr">
@@ -22158,7 +22158,7 @@
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H168" s="12" t="inlineStr">
@@ -22231,7 +22231,7 @@
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H169" s="12" t="inlineStr">
@@ -22304,7 +22304,7 @@
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H170" s="12" t="inlineStr">
@@ -22376,7 +22376,7 @@
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H171" s="12" t="inlineStr">
@@ -22445,7 +22445,7 @@
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H172" s="12" t="inlineStr">
@@ -22521,7 +22521,7 @@
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H173" s="12" t="inlineStr">
@@ -22597,7 +22597,7 @@
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H174" s="12" t="inlineStr">
@@ -22670,7 +22670,7 @@
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H175" s="12" t="inlineStr">
@@ -22680,7 +22680,7 @@
       </c>
       <c r="I175" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J175" s="12" t="inlineStr">
@@ -22746,7 +22746,7 @@
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H176" s="12" t="inlineStr">
@@ -22756,7 +22756,7 @@
       </c>
       <c r="I176" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J176" s="12" t="inlineStr">
@@ -22822,7 +22822,7 @@
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H177" s="12" t="inlineStr">
@@ -22833,7 +22833,7 @@
       <c r="I177" s="12" t="inlineStr">
         <is>
           <t>Cashiering re-application is switched off in SIT (port default).
-Data: TD-OP-02 Booked demo invoices</t>
+Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J177" s="12" t="inlineStr">
@@ -22900,7 +22900,7 @@
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H178" s="12" t="inlineStr">
@@ -22973,7 +22973,7 @@
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H179" s="12" t="inlineStr">
@@ -23041,7 +23041,7 @@
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H180" s="12" t="inlineStr">
@@ -23110,7 +23110,7 @@
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H181" s="12" t="inlineStr">
@@ -23186,7 +23186,7 @@
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H182" s="12" t="inlineStr">
@@ -23259,7 +23259,7 @@
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H183" s="12" t="inlineStr">
@@ -23332,7 +23332,7 @@
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H184" s="12" t="inlineStr">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H185" s="12" t="inlineStr">
@@ -23485,7 +23485,7 @@
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H186" s="12" t="inlineStr">
@@ -23562,7 +23562,7 @@
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H187" s="12" t="inlineStr">
@@ -23634,7 +23634,7 @@
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H188" s="12" t="inlineStr">
@@ -23654,7 +23654,7 @@
       </c>
       <c r="K188" s="12" t="inlineStr">
         <is>
-          <t>The four demo requests are listed; the link opens Invoice 360.</t>
+          <t>The four seed requests are listed; the link opens Invoice 360.</t>
         </is>
       </c>
       <c r="L188" s="12" t="inlineStr">
@@ -23710,7 +23710,7 @@
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H189" s="12" t="inlineStr">
@@ -23787,7 +23787,7 @@
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="H190" s="12" t="inlineStr">
@@ -23863,7 +23863,7 @@
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H191" s="12" t="inlineStr">
@@ -23939,7 +23939,7 @@
       </c>
       <c r="G192" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H192" s="12" t="inlineStr">
@@ -24011,7 +24011,7 @@
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H193" s="12" t="inlineStr">
@@ -24027,7 +24027,7 @@
       </c>
       <c r="J193" s="12" t="inlineStr">
         <is>
-          <t>1. Keep the demo schedule of INS-MGIC on day 5; run PRODUCTION_EXTRACT for 5 and 6 October (clock moved).</t>
+          <t>1. Keep the seed schedule of INS-MGIC on day 5; run PRODUCTION_EXTRACT for 5 and 6 October (clock moved).</t>
         </is>
       </c>
       <c r="K193" s="12" t="inlineStr">
@@ -24088,7 +24088,7 @@
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H194" s="12" t="inlineStr">
@@ -24165,7 +24165,7 @@
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H195" s="12" t="inlineStr">
@@ -24241,7 +24241,7 @@
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H196" s="12" t="inlineStr">
@@ -24314,7 +24314,7 @@
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H197" s="12" t="inlineStr">
@@ -24387,7 +24387,7 @@
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H198" s="12" t="inlineStr">
@@ -24459,7 +24459,7 @@
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H199" s="12" t="inlineStr">
@@ -24531,7 +24531,7 @@
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H200" s="12" t="inlineStr">
@@ -24603,7 +24603,7 @@
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H201" s="12" t="inlineStr">
@@ -24679,7 +24679,7 @@
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H202" s="12" t="inlineStr">
@@ -24753,7 +24753,7 @@
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H203" s="12" t="inlineStr">
@@ -24830,7 +24830,7 @@
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H204" s="12" t="inlineStr">
@@ -24906,7 +24906,7 @@
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H205" s="12" t="inlineStr">
@@ -24983,7 +24983,7 @@
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H206" s="12" t="inlineStr">
@@ -25060,7 +25060,7 @@
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H207" s="12" t="inlineStr">
@@ -25137,7 +25137,7 @@
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H208" s="12" t="inlineStr">
@@ -25213,7 +25213,7 @@
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H209" s="12" t="inlineStr">
@@ -25289,7 +25289,7 @@
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H210" s="12" t="inlineStr">
@@ -25362,7 +25362,7 @@
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H211" s="12" t="inlineStr">
@@ -25438,7 +25438,7 @@
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H212" s="12" t="inlineStr">
@@ -25514,7 +25514,7 @@
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H213" s="12" t="inlineStr">
@@ -25529,7 +25529,7 @@
       </c>
       <c r="J213" s="12" t="inlineStr">
         <is>
-          <t>1. Look for the demo policy BDOI never booked.</t>
+          <t>1. Look for the seed policy BDOI never booked.</t>
         </is>
       </c>
       <c r="K213" s="12" t="inlineStr">
@@ -25586,7 +25586,7 @@
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H214" s="12" t="inlineStr">
@@ -25662,7 +25662,7 @@
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H215" s="12" t="inlineStr">
@@ -25735,7 +25735,7 @@
       </c>
       <c r="G216" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H216" s="12" t="inlineStr">
@@ -25808,7 +25808,7 @@
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H217" s="12" t="inlineStr">
@@ -25884,7 +25884,7 @@
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H218" s="12" t="inlineStr">
@@ -25956,7 +25956,7 @@
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H219" s="12" t="inlineStr">
@@ -26032,7 +26032,7 @@
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H220" s="12" t="inlineStr">
@@ -26047,7 +26047,7 @@
       </c>
       <c r="J220" s="12" t="inlineStr">
         <is>
-          <t>1. Set For closure on every open item of the demo cycle.</t>
+          <t>1. Set For closure on every open item of the seed cycle.</t>
         </is>
       </c>
       <c r="K220" s="12" t="inlineStr">
@@ -26108,7 +26108,7 @@
       </c>
       <c r="G221" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H221" s="12" t="inlineStr">
@@ -26185,7 +26185,7 @@
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H222" s="12" t="inlineStr">
@@ -26200,7 +26200,7 @@
       </c>
       <c r="J222" s="12" t="inlineStr">
         <is>
-          <t>1. Run PRC-SUMMARY for the demo cycle; compare with the cycle tiles.</t>
+          <t>1. Run PRC-SUMMARY for the seed cycle; compare with the cycle tiles.</t>
         </is>
       </c>
       <c r="K222" s="12" t="inlineStr">
@@ -26261,7 +26261,7 @@
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="H223" s="12" t="inlineStr">
@@ -26337,7 +26337,7 @@
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H224" s="12" t="inlineStr">
@@ -26410,7 +26410,7 @@
       </c>
       <c r="G225" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="H225" s="12" t="inlineStr">
@@ -26486,7 +26486,7 @@
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="H226" s="12" t="inlineStr">
@@ -26563,7 +26563,7 @@
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="H227" s="12" t="inlineStr">
@@ -26636,7 +26636,7 @@
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="H228" s="12" t="inlineStr">
@@ -26712,7 +26712,7 @@
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="H229" s="12" t="inlineStr">
@@ -26788,7 +26788,7 @@
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="H230" s="12" t="inlineStr">
@@ -26864,7 +26864,7 @@
       </c>
       <c r="G231" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="H231" s="12" t="inlineStr">
@@ -26879,7 +26879,7 @@
       </c>
       <c r="J231" s="12" t="inlineStr">
         <is>
-          <t>1. Confirm the billed demo account again.</t>
+          <t>1. Confirm the billed seed account again.</t>
         </is>
       </c>
       <c r="K231" s="12" t="inlineStr">
@@ -26937,7 +26937,7 @@
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="H232" s="12" t="inlineStr">
@@ -27013,7 +27013,7 @@
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="H233" s="12" t="inlineStr">
@@ -27086,7 +27086,7 @@
       </c>
       <c r="G234" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="H234" s="12" t="inlineStr">
@@ -27101,7 +27101,7 @@
       </c>
       <c r="J234" s="12" t="inlineStr">
         <is>
-          <t>1. Send the demo billing again.</t>
+          <t>1. Send the seed billing again.</t>
         </is>
       </c>
       <c r="K234" s="12" t="inlineStr">
@@ -27159,7 +27159,7 @@
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="H235" s="12" t="inlineStr">
@@ -27232,7 +27232,7 @@
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="H236" s="12" t="inlineStr">
@@ -27308,7 +27308,7 @@
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H237" s="12" t="inlineStr">
@@ -27318,7 +27318,7 @@
       </c>
       <c r="I237" s="12" t="inlineStr">
         <is>
-          <t>The demo billing sent 11 working days ago (date moved in SIT).
+          <t>The seed billing sent 11 working days ago (date moved in SIT).
 Data: TD-OP-07 Commission storyline; TD-OP-08 Operations files</t>
         </is>
       </c>
@@ -27385,7 +27385,7 @@
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="H238" s="12" t="inlineStr">
@@ -27462,7 +27462,7 @@
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="H239" s="12" t="inlineStr">
@@ -27477,7 +27477,7 @@
       </c>
       <c r="J239" s="12" t="inlineStr">
         <is>
-          <t>1. Record APPROVED for the demo billing; Collect with bank account 1111 and today's date.</t>
+          <t>1. Record APPROVED for the seed billing; Collect with bank account 1111 and today's date.</t>
         </is>
       </c>
       <c r="K239" s="12" t="inlineStr">
@@ -27538,7 +27538,7 @@
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="H240" s="12" t="inlineStr">
@@ -27611,7 +27611,7 @@
       </c>
       <c r="G241" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="H241" s="12" t="inlineStr">
@@ -27684,7 +27684,7 @@
       </c>
       <c r="G242" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="H242" s="12" t="inlineStr">
@@ -27760,7 +27760,7 @@
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_TL – Commission TL / TH (demo user commtl)</t>
+          <t>COMMREC_TL – Commission TL / TH (SIT/UAT user commtl)</t>
         </is>
       </c>
       <c r="H243" s="12" t="inlineStr">
@@ -27836,7 +27836,7 @@
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_TL – Commission TL / TH (demo user commtl)</t>
+          <t>COMMREC_TL – Commission TL / TH (SIT/UAT user commtl)</t>
         </is>
       </c>
       <c r="H244" s="12" t="inlineStr">
@@ -27912,7 +27912,7 @@
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_TL – Commission TL / TH (demo user commtl)</t>
+          <t>COMMREC_TL – Commission TL / TH (SIT/UAT user commtl)</t>
         </is>
       </c>
       <c r="H245" s="12" t="inlineStr">
@@ -27985,7 +27985,7 @@
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_TL – Commission TL / TH (demo user commtl)</t>
+          <t>COMMREC_TL – Commission TL / TH (SIT/UAT user commtl)</t>
         </is>
       </c>
       <c r="H246" s="12" t="inlineStr">
@@ -28058,7 +28058,7 @@
       </c>
       <c r="G247" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="H247" s="12" t="inlineStr">
@@ -28131,7 +28131,7 @@
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="H248" s="12" t="inlineStr">
@@ -28207,7 +28207,7 @@
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
-          <t>COMPTROLLERSHIP – Comptrollership (demo user comptrol)</t>
+          <t>COMPTROLLERSHIP – Comptrollership (SIT/UAT user comptrol)</t>
         </is>
       </c>
       <c r="H249" s="12" t="inlineStr">
@@ -28280,7 +28280,7 @@
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="H250" s="12" t="inlineStr">
@@ -28290,7 +28290,7 @@
       </c>
       <c r="I250" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J250" s="12" t="inlineStr">
@@ -28356,7 +28356,7 @@
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="H251" s="12" t="inlineStr">
@@ -28366,7 +28366,7 @@
       </c>
       <c r="I251" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J251" s="12" t="inlineStr">
@@ -28432,7 +28432,7 @@
       </c>
       <c r="G252" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="H252" s="12" t="inlineStr">
@@ -28442,7 +28442,7 @@
       </c>
       <c r="I252" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J252" s="12" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="G253" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="H253" s="12" t="inlineStr">
@@ -28580,7 +28580,7 @@
       </c>
       <c r="G254" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H254" s="12" t="inlineStr">
@@ -28657,7 +28657,7 @@
       </c>
       <c r="G255" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H255" s="12" t="inlineStr">
@@ -28672,7 +28672,7 @@
       </c>
       <c r="J255" s="12" t="inlineStr">
         <is>
-          <t>1. Open the remitted demo batch; Send via Email to the insurer's test mailbox.</t>
+          <t>1. Open the remitted seed batch; Send via Email to the insurer's test mailbox.</t>
         </is>
       </c>
       <c r="K255" s="12" t="inlineStr">
@@ -28733,7 +28733,7 @@
       </c>
       <c r="G256" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H256" s="12" t="inlineStr">
@@ -28810,7 +28810,7 @@
       </c>
       <c r="G257" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H257" s="12" t="inlineStr">
@@ -28873,7 +28873,7 @@
       </c>
       <c r="E258" s="12" t="inlineStr">
         <is>
-          <t>Approve the demo hold</t>
+          <t>Approve the seed hold</t>
         </is>
       </c>
       <c r="F258" s="12" t="inlineStr">
@@ -28883,7 +28883,7 @@
       </c>
       <c r="G258" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H258" s="12" t="inlineStr">
@@ -28893,7 +28893,7 @@
       </c>
       <c r="I258" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices; TD-OP-04 Remittance storyline</t>
+          <t>Data: TD-OP-02 Booked seed invoices; TD-OP-04 Remittance storyline</t>
         </is>
       </c>
       <c r="J258" s="12" t="inlineStr">
@@ -28959,7 +28959,7 @@
       </c>
       <c r="G259" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="H259" s="12" t="inlineStr">
@@ -28970,7 +28970,7 @@
       <c r="I259" s="12" t="inlineStr">
         <is>
           <t>mkttl raised a hold request.
-Data: TD-OP-02 Booked demo invoices; TD-OP-04 Remittance storyline</t>
+Data: TD-OP-02 Booked seed invoices; TD-OP-04 Remittance storyline</t>
         </is>
       </c>
       <c r="J259" s="12" t="inlineStr">
@@ -29037,7 +29037,7 @@
       </c>
       <c r="G260" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H260" s="12" t="inlineStr">
@@ -29048,7 +29048,7 @@
       <c r="I260" s="12" t="inlineStr">
         <is>
           <t>The hold's until date set to yesterday.
-Data: TD-OP-02 Booked demo invoices; TD-OP-04 Remittance storyline</t>
+Data: TD-OP-02 Booked seed invoices; TD-OP-04 Remittance storyline</t>
         </is>
       </c>
       <c r="J260" s="12" t="inlineStr">
@@ -29114,7 +29114,7 @@
       </c>
       <c r="G261" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H261" s="12" t="inlineStr">
@@ -29124,7 +29124,7 @@
       </c>
       <c r="I261" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices; TD-OP-04 Remittance storyline</t>
+          <t>Data: TD-OP-02 Booked seed invoices; TD-OP-04 Remittance storyline</t>
         </is>
       </c>
       <c r="J261" s="12" t="inlineStr">
@@ -29187,7 +29187,7 @@
       </c>
       <c r="G262" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H262" s="12" t="inlineStr">
@@ -29197,7 +29197,7 @@
       </c>
       <c r="I262" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices; TD-OP-04 Remittance storyline</t>
+          <t>Data: TD-OP-02 Booked seed invoices; TD-OP-04 Remittance storyline</t>
         </is>
       </c>
       <c r="J262" s="12" t="inlineStr">
@@ -29260,7 +29260,7 @@
       </c>
       <c r="G263" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H263" s="12" t="inlineStr">
@@ -29270,7 +29270,7 @@
       </c>
       <c r="I263" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices; TD-OP-04 Remittance storyline</t>
+          <t>Data: TD-OP-02 Booked seed invoices; TD-OP-04 Remittance storyline</t>
         </is>
       </c>
       <c r="J263" s="12" t="inlineStr">
@@ -29333,7 +29333,7 @@
       </c>
       <c r="G264" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H264" s="12" t="inlineStr">
@@ -29344,7 +29344,7 @@
       <c r="I264" s="12" t="inlineStr">
         <is>
           <t>An invoice paid by check yesterday.
-Data: TD-OP-02 Booked demo invoices</t>
+Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J264" s="12" t="inlineStr">
@@ -29407,7 +29407,7 @@
       </c>
       <c r="G265" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H265" s="12" t="inlineStr">
@@ -29417,7 +29417,7 @@
       </c>
       <c r="I265" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J265" s="12" t="inlineStr">
@@ -29483,7 +29483,7 @@
       </c>
       <c r="G266" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H266" s="12" t="inlineStr">
@@ -29493,7 +29493,7 @@
       </c>
       <c r="I266" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J266" s="12" t="inlineStr">
@@ -29556,7 +29556,7 @@
       </c>
       <c r="G267" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H267" s="12" t="inlineStr">
@@ -29566,7 +29566,7 @@
       </c>
       <c r="I267" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J267" s="12" t="inlineStr">
@@ -29632,7 +29632,7 @@
       </c>
       <c r="G268" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H268" s="12" t="inlineStr">
@@ -29642,7 +29642,7 @@
       </c>
       <c r="I268" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J268" s="12" t="inlineStr">
@@ -29709,7 +29709,7 @@
       </c>
       <c r="G269" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H269" s="12" t="inlineStr">
@@ -29719,7 +29719,7 @@
       </c>
       <c r="I269" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J269" s="12" t="inlineStr">
@@ -29782,7 +29782,7 @@
       </c>
       <c r="G270" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H270" s="12" t="inlineStr">
@@ -29858,7 +29858,7 @@
       </c>
       <c r="G271" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="H271" s="12" t="inlineStr">
@@ -29935,7 +29935,7 @@
       </c>
       <c r="G272" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H272" s="12" t="inlineStr">
@@ -30011,7 +30011,7 @@
       </c>
       <c r="G273" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H273" s="12" t="inlineStr">
@@ -30088,7 +30088,7 @@
       </c>
       <c r="G274" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="H274" s="12" t="inlineStr">
@@ -30161,7 +30161,7 @@
       </c>
       <c r="G275" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H275" s="12" t="inlineStr">
@@ -30237,7 +30237,7 @@
       </c>
       <c r="G276" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H276" s="12" t="inlineStr">
@@ -30310,7 +30310,7 @@
       </c>
       <c r="G277" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H277" s="12" t="inlineStr">
@@ -30386,7 +30386,7 @@
       </c>
       <c r="G278" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H278" s="12" t="inlineStr">
@@ -30462,7 +30462,7 @@
       </c>
       <c r="G279" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H279" s="12" t="inlineStr">
@@ -30539,7 +30539,7 @@
       </c>
       <c r="G280" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H280" s="12" t="inlineStr">
@@ -30615,7 +30615,7 @@
       </c>
       <c r="G281" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H281" s="12" t="inlineStr">
@@ -30691,7 +30691,7 @@
       </c>
       <c r="G282" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="H282" s="12" t="inlineStr">
@@ -30768,7 +30768,7 @@
       </c>
       <c r="G283" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H283" s="12" t="inlineStr">
@@ -30778,7 +30778,7 @@
       </c>
       <c r="I283" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J283" s="12" t="inlineStr">
@@ -30844,7 +30844,7 @@
       </c>
       <c r="G284" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="H284" s="12" t="inlineStr">
@@ -30854,7 +30854,7 @@
       </c>
       <c r="I284" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-OP-02 Booked demo invoices</t>
+          <t>Data: TD-OP-02 Booked seed invoices</t>
         </is>
       </c>
       <c r="J284" s="12" t="inlineStr">
@@ -41049,17 +41049,17 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Demo users and roles</t>
+          <t>SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>cashier (CASHIER, Head Office), cashbr (CASHIER, Cebu branch), cashtl (CASHIER_TL), remit (REMIT_PROCESSOR), remittl (REMIT_TL), recon (RECON_HANDLER), adjust (ADJUSTMENT), adjtl (ADJUSTMENT_TL), commrec (COMMREC_HANDLER), commtl (COMMREC_TL), mktcoll (MKT_COLLECTION), mkttl (MKT_TL), comptrol (COMPTROLLERSHIP), disb (DISBURSEMENT), admin (SYSADMIN), auditor (AUDITOR). The demo password is issued by the test lead.</t>
+          <t>cashier (CASHIER, Head Office), cashbr (CASHIER, Cebu branch), cashtl (CASHIER_TL), remit (REMIT_PROCESSOR), remittl (REMIT_TL), recon (RECON_HANDLER), adjust (ADJUSTMENT), adjtl (ADJUSTMENT_TL), commrec (COMMREC_HANDLER), commtl (COMMREC_TL), mktcoll (MKT_COLLECTION), mkttl (MKT_TL), comptrol (COMPTROLLERSHIP), disb (DISBURSEMENT), admin (SYSADMIN), auditor (AUDITOR). The SIT/UAT password is issued by the test lead.</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Demo seeds V990 (Operations users), V980 (adjust, mkttl), V900 (admin, auditor); grants V760</t>
+          <t>Seeds V990 (Operations users), V980 (adjust, mkttl), V900 (admin, auditor); grants V760</t>
         </is>
       </c>
       <c r="E5" s="12" t="n">
@@ -41074,7 +41074,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Booked demo invoices</t>
+          <t>Booked seed invoices</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -41084,7 +41084,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Booking demo data (V988 and BookingDemoData), copied into the invoice ledger by the booking feed</t>
+          <t>Booking seed data (V988 and BookingSeedData), copied into the invoice ledger by the booking feed</t>
         </is>
       </c>
       <c r="E6" s="12" t="n">
@@ -41109,7 +41109,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V991 and CashieringDemoData</t>
+          <t>Seed V991 and CashieringSeedData</t>
         </is>
       </c>
       <c r="E7" s="12" t="n">
@@ -41134,7 +41134,7 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V992 and RemittanceDemoData</t>
+          <t>Seed V992 and RemittanceSeedData</t>
         </is>
       </c>
       <c r="E8" s="12" t="n">
@@ -41154,12 +41154,12 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>September 2026 register of INS-MGIC extracted, sent and answered; cycle RECONCILING with a gross premium discrepancy on ARN-2026-940002 and one insurer policy never booked; monthly schedules on the 5th; demo lists of company concerned and dispositions</t>
+          <t>September 2026 register of INS-MGIC extracted, sent and answered; cycle RECONCILING with a gross premium discrepancy on ARN-2026-940002 and one insurer policy never booked; monthly schedules on the 5th; seed lists of company concerned and dispositions</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V993 and ProdReconDemoData</t>
+          <t>Seed V993 and ProdReconSeedData</t>
         </is>
       </c>
       <c r="E9" s="12" t="n">
@@ -41184,7 +41184,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V994 and AdjustmentDemoData</t>
+          <t>Seed V994 and AdjustmentSeedData</t>
         </is>
       </c>
       <c r="E10" s="12" t="n">
@@ -41209,7 +41209,7 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V995 and CommissionDemoData</t>
+          <t>Seed V995 and CommissionSeedData</t>
         </is>
       </c>
       <c r="E11" s="12" t="n">
@@ -41234,7 +41234,7 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Prepared by the test lead from the wizard templates and the layouts of the demo files; masked names</t>
+          <t>Prepared by the test lead from the wizard templates and the layouts of the seed files; masked names</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
@@ -41254,12 +41254,12 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>A USD invoice of a demo client and the BOOK rate of the receipt date (2 decimals)</t>
+          <t>A USD invoice of a seed client and the BOOK rate of the receipt date (2 decimals)</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V990 (BOOK rates from the demo SPOT rates)</t>
+          <t>Seed V990 (BOOK rates from the seed SPOT rates)</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
@@ -41284,7 +41284,7 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Created by the demo storylines above</t>
+          <t>Created by the seed storylines above</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
@@ -41458,7 +41458,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -41509,7 +41509,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -41560,7 +41560,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -41611,7 +41611,7 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -41662,7 +41662,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -41713,7 +41713,7 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
@@ -41764,7 +41764,7 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -41815,7 +41815,7 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
@@ -41866,7 +41866,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -41913,7 +41913,7 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>CASHIER_TL – Cashiering TL / TH (demo user cashtl)</t>
+          <t>CASHIER_TL – Cashiering TL / TH (SIT/UAT user cashtl)</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -41960,7 +41960,7 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -42007,7 +42007,7 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -42054,7 +42054,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -42101,7 +42101,7 @@
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>CASHIER_TL – Cashiering TL / TH (demo user cashtl)</t>
+          <t>CASHIER_TL – Cashiering TL / TH (SIT/UAT user cashtl)</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
@@ -42148,7 +42148,7 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -42195,7 +42195,7 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -42242,7 +42242,7 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>CASHIER_TL – Cashiering TL / TH (demo user cashtl)</t>
+          <t>CASHIER_TL – Cashiering TL / TH (SIT/UAT user cashtl)</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -42289,7 +42289,7 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
@@ -42336,7 +42336,7 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -42383,7 +42383,7 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance TL / TH (demo user remittl)</t>
+          <t>REMIT_TL – Remittance TL / TH (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -42430,7 +42430,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -42477,7 +42477,7 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
@@ -42524,7 +42524,7 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -42571,7 +42571,7 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance TL / TH (demo user remittl)</t>
+          <t>REMIT_TL – Remittance TL / TH (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -42618,7 +42618,7 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -42665,7 +42665,7 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -42712,7 +42712,7 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -42763,7 +42763,7 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -42814,7 +42814,7 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -42865,7 +42865,7 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -42916,7 +42916,7 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
@@ -42967,7 +42967,7 @@
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -43018,7 +43018,7 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance TL / TH (demo user remittl)</t>
+          <t>REMIT_TL – Remittance TL / TH (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
@@ -43069,7 +43069,7 @@
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
@@ -43116,7 +43116,7 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
@@ -43163,7 +43163,7 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
@@ -43210,7 +43210,7 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
@@ -43257,7 +43257,7 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
@@ -43308,7 +43308,7 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
@@ -43359,7 +43359,7 @@
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
@@ -43410,7 +43410,7 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
@@ -43461,7 +43461,7 @@
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
@@ -43508,7 +43508,7 @@
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>MKT_TL – Marketing TL / UH (demo user mkttl)</t>
+          <t>MKT_TL – Marketing TL / UH (SIT/UAT user mkttl)</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
@@ -43555,7 +43555,7 @@
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
@@ -43602,7 +43602,7 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
@@ -43649,7 +43649,7 @@
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
@@ -43696,7 +43696,7 @@
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT_TL – Adjustment TL (demo user adjtl)</t>
+          <t>ADJUSTMENT_TL – Adjustment TL (SIT/UAT user adjtl)</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
@@ -43743,7 +43743,7 @@
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
@@ -43790,7 +43790,7 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
@@ -43837,7 +43837,7 @@
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT_TL – Adjustment TL (demo user adjtl)</t>
+          <t>ADJUSTMENT_TL – Adjustment TL (SIT/UAT user adjtl)</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
@@ -43884,7 +43884,7 @@
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
@@ -43931,7 +43931,7 @@
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
@@ -43982,7 +43982,7 @@
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_TL – Commission TL / TH (demo user commtl)</t>
+          <t>COMMREC_TL – Commission TL / TH (SIT/UAT user commtl)</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
@@ -44033,7 +44033,7 @@
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
@@ -44084,7 +44084,7 @@
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
@@ -44135,7 +44135,7 @@
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_TL – Commission TL / TH (demo user commtl)</t>
+          <t>COMMREC_TL – Commission TL / TH (SIT/UAT user commtl)</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr">
@@ -44182,7 +44182,7 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
@@ -44229,7 +44229,7 @@
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>COMPTROLLERSHIP – Comptrollership (demo user comptrol)</t>
+          <t>COMPTROLLERSHIP – Comptrollership (SIT/UAT user comptrol)</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr">
@@ -44276,7 +44276,7 @@
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
@@ -44323,7 +44323,7 @@
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
@@ -44370,7 +44370,7 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance TL / TH (demo user remittl)</t>
+          <t>REMIT_TL – Remittance TL / TH (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
@@ -44417,7 +44417,7 @@
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_TL – Commission TL / TH (demo user commtl)</t>
+          <t>COMMREC_TL – Commission TL / TH (SIT/UAT user commtl)</t>
         </is>
       </c>
       <c r="F66" s="12" t="inlineStr">
@@ -44464,7 +44464,7 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>SYSADMIN – System Administrator (demo user admin)</t>
+          <t>SYSADMIN – System Administrator (SIT/UAT user admin)</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
@@ -44515,7 +44515,7 @@
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr">
@@ -44566,7 +44566,7 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance TL / TH (demo user remittl)</t>
+          <t>REMIT_TL – Remittance TL / TH (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
@@ -44617,7 +44617,7 @@
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (Head Office) (demo user cashier)</t>
+          <t>CASHIER – Cashier (Head Office) (SIT/UAT user cashier)</t>
         </is>
       </c>
       <c r="F70" s="12" t="inlineStr">
@@ -44664,7 +44664,7 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>REMIT_PROCESSOR – Remittance Processor (demo user remit)</t>
+          <t>REMIT_PROCESSOR – Remittance Processor (SIT/UAT user remit)</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
@@ -44711,7 +44711,7 @@
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>RECON_HANDLER – Production Reconciliation Handler (demo user recon)</t>
+          <t>RECON_HANDLER – Production Reconciliation Handler (SIT/UAT user recon)</t>
         </is>
       </c>
       <c r="F72" s="12" t="inlineStr">
@@ -44758,7 +44758,7 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>ADJUSTMENT – Adjustment Processor (demo user adjust)</t>
+          <t>ADJUSTMENT – Adjustment Processor (SIT/UAT user adjust)</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
@@ -44805,7 +44805,7 @@
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>COMMREC_HANDLER – Commission Handler (demo user commrec)</t>
+          <t>COMMREC_HANDLER – Commission Handler (SIT/UAT user commrec)</t>
         </is>
       </c>
       <c r="F74" s="12" t="inlineStr">
@@ -44852,7 +44852,7 @@
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>MKT_COLLECTION – Marketing Collection (demo user mktcoll)</t>
+          <t>MKT_COLLECTION – Marketing Collection (SIT/UAT user mktcoll)</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
@@ -44899,7 +44899,7 @@
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="F76" s="12" t="inlineStr">
@@ -44946,7 +44946,7 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
